--- a/customer address raj.xlsx
+++ b/customer address raj.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2218"/>
+  <dimension ref="A1:E2223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -27218,12 +27218,12 @@
       </c>
       <c r="B995" s="8" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>Heena.Mirza@larsentoubro.com</t>
         </is>
       </c>
       <c r="C995" s="9" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>8976246009</t>
         </is>
       </c>
       <c r="D995" s="7" t="inlineStr">
@@ -29086,7 +29086,7 @@
       </c>
       <c r="C1064" s="9" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>91-70242-66351 / +91 - 731 - 4068777</t>
         </is>
       </c>
       <c r="D1064" s="7" t="inlineStr">
@@ -29096,7 +29096,10 @@
       </c>
       <c r="E1064" s="7" t="inlineStr">
         <is>
-          <t>PLOT NO. B/9, RADHIKA KUNJ COLONYLIG LINK ROAD, NEAR RING ROAD KHAJRANAINDORE - 452011, MADHYA PRADESH.</t>
+          <t>PLOT NO. B/9 RADHIKA KUNJ,
+COLONYLIG LINK ROAD, 
+NEAR RING ROAD KHAJRANA,
+INDORE - 452011, MADHYA PRADESH.</t>
         </is>
       </c>
     </row>
@@ -60174,6 +60177,144 @@
       <c r="E2218" t="inlineStr">
         <is>
           <t>New Modern Facility, Hinjawadi Phase 2, Pune</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>SEROS SHIPPING PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>Himanshu.Shah@equipto.co.in</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>9925246153</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>24AADCE6558P1Z3</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>INNOV8, UNIT NO 1303, 
+Q2, AURUM Q PARK,
+THANE BELAPUR ROAD,
+GHANSOLI, NAVI MUMBAI – 400 710</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>TEST NEW MANUAL CORP</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>updated@manualcorp.com</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>9999988888</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>24AAACT1234M1Z5</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>Updated Address Street 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>AUTO SYNC CLIENT PVT LTD</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>sales@autosync.com</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>022-27412345</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>27AAACA9999Z1Z0</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>Plot 99, MIDC Taloja, Navi Mumbai</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>VVS Enterprises Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>svishwanath@vvsenterprisesindia.com</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>Nil</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>Nil</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>Malad (W), Mumbai – 400064</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>raajjj</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>Nil</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>Nil</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>Nil</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>raajjjjj</t>
         </is>
       </c>
     </row>
